--- a/XYZ_analysis.xlsx
+++ b/XYZ_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>SKU</t>
   </si>
@@ -100,13 +100,10 @@
     <t>Z (Erratic)</t>
   </si>
   <si>
-    <t>AY</t>
-  </si>
-  <si>
-    <t>BZ</t>
-  </si>
-  <si>
-    <t>CY</t>
+    <t>Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total </t>
   </si>
 </sst>
 </file>
@@ -194,7 +191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr defaultRowHeight="14.0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.55"/>
@@ -661,6 +658,33 @@
         <v>24</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <extLst/>
 </worksheet>
@@ -668,15 +692,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.0" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.24"/>
-    <col min="2" max="2" width="13.24"/>
-    <col min="3" max="3" width="13.24"/>
-    <col min="4" max="4" width="13.24"/>
-    <col min="5" max="18" width="13.24"/>
-    <col min="19" max="19" width="13.24"/>
+    <col min="1" max="19" width="13.24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -690,16 +709,29 @@
       <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
+      <c r="B2">
+        <f>COUNTIF('Sheet1'!$S:$S,"AX")</f>
+        <v>1.0</v>
+      </c>
+      <c r="C2">
+        <f>COUNTIF('Sheet1'!$S:$S,"AY")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D2">
+        <f>COUNTIF('Sheet1'!$S:$S,"AZ")</f>
+        <v>1.0</v>
+      </c>
+      <c r="E2">
+        <f t="shared" ref="E2:E5" si="3">SUM(B2:D2)</f>
+        <v>2.0</v>
       </c>
     </row>
     <row r="3">
@@ -707,14 +739,20 @@
         <v>15</v>
       </c>
       <c r="B3" s="5">
-        <f>COUNTIF('Sheet1'!$S:$S,"AX")</f>
+        <f>COUNTIF('Sheet1'!$S:$S,"BX")</f>
         <v>1.0</v>
       </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
+      <c r="C3" s="5">
+        <f>COUNTIF('Sheet1'!$S:$S,"BY")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D3">
+        <f>COUNTIF('Sheet1'!$S:$S,"BZ")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="5">
+        <f t="shared" si="3"/>
+        <v>2.0</v>
       </c>
     </row>
     <row r="4">
@@ -722,15 +760,157 @@
         <v>21</v>
       </c>
       <c r="B4" s="5">
-        <f>COUNTIF('Sheet1'!$S:$S,"AX")</f>
+        <f>COUNTIF('Sheet1'!$S:$S,"CX")</f>
         <v>1.0</v>
       </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
+      <c r="C4" s="5">
+        <f>COUNTIF('Sheet1'!$S:$S,"CY")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D4">
+        <f>COUNTIF('Sheet1'!$S:$S,"CZ")</f>
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" si="3"/>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B2:B4)</f>
+        <v>3.0</v>
+      </c>
+      <c r="C5" s="5">
+        <f>SUM(C2:C4)</f>
+        <v>1.0</v>
+      </c>
+      <c r="D5" s="5">
+        <f>SUM(D2:D4)</f>
+        <v>2.0</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" si="3"/>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3">
+        <f t="shared" ref="B8:B10" si="13">IF($E$5=0,0,(B2/$E$5)*100)</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="C8" s="3">
+        <f t="shared" ref="C8:C10" si="14">IF($E$5=0,0,(C2/$E$5)*100)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" ref="D8:D10" si="15">IF($E$5=0,0,(D2/$E$5)*100)</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="E8">
+        <f t="shared" ref="E8:E11" si="16">SUM(B8:D8)</f>
+        <v>33.3333333333334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3">
+        <f t="shared" si="13"/>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="C9" s="3">
+        <f t="shared" si="14"/>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="15"/>
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="5">
+        <f t="shared" si="16"/>
+        <v>33.3333333333334</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="3">
+        <f t="shared" si="13"/>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="C10" s="3">
+        <f t="shared" si="14"/>
+        <v>0.0</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="15"/>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="E10" s="5">
+        <f t="shared" si="16"/>
+        <v>33.3333333333334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11">
+        <f>SUM(B8:B10)</f>
+        <v>50.0000000000001</v>
+      </c>
+      <c r="C11" s="5">
+        <f>SUM(C8:C10)</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="D11" s="5">
+        <f>SUM(D8:D10)</f>
+        <v>33.3333333333334</v>
+      </c>
+      <c r="E11" s="5">
+        <f t="shared" si="16"/>
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
     </row>
   </sheetData>
   <extLst/>
